--- a/src/nist_gas_srm/core/data/template.xlsx
+++ b/src/nist_gas_srm/core/data/template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:r="http://purl.oclc.org/ooxml/officeDocument/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2" conformance="strict">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10817"/>
   <workbookPr dateCompatibility="0" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wpk/gits/nist-gas-srm-certificate/nist-gas-srm/tmp/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wpk/gits/nist-gas-srm-certificate/nist-gas-srm/src/nist_gas_srm/core/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{5B73E5E8-8711-444E-984D-EA323EA32479}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{C4D6DA55-042D-5347-AA59-864A306A83A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="16920" yWindow="600" windowWidth="32760" windowHeight="22400" tabRatio="858" activeTab="4" xr2:uid="{39D6750C-C4B1-7443-AD53-6D53C3AA6660}"/>
+    <workbookView xWindow="16920" yWindow="600" windowWidth="32760" windowHeight="22400" tabRatio="858" xr2:uid="{39D6750C-C4B1-7443-AD53-6D53C3AA6660}"/>
   </bookViews>
   <sheets>
     <sheet name="Ratio Data" sheetId="1" r:id="rId1"/>
@@ -75,7 +75,7 @@
     <author>Microsoft Office User</author>
   </authors>
   <commentList>
-    <comment ref="AB3" authorId="0" shapeId="3073" xr:uid="{C60AE0F9-2503-0B4F-B866-CF997827A49D}">
+    <comment ref="AB3" authorId="0" shapeId="2049" xr:uid="{C60AE0F9-2503-0B4F-B866-CF997827A49D}">
       <text>
         <r>
           <rPr>
@@ -134,7 +134,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" count="1576" uniqueCount="401">
+<sst xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" count="1563" uniqueCount="400">
   <si>
     <t>%</t>
   </si>
@@ -1304,9 +1304,6 @@
   </si>
   <si>
     <t>48-I-12</t>
-  </si>
-  <si>
-    <t>48-I-13</t>
   </si>
   <si>
     <t>48-I-14</t>
@@ -2794,7 +2791,7 @@
       <alignment wrapText="1"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="500">
+  <cellXfs count="499">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3848,7 +3845,6 @@
     <xf numFmtId="164" fontId="37" fillId="11" borderId="47" xfId="5" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="170" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -4499,10 +4495,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="3073" name="Comment 1" hidden="1">
+            <xdr:cNvPr id="2049" name="Comment 1" hidden="1">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D273AEFC-C778-C982-CB02-90EBC0CE84FB}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EEDC63CC-A035-88E8-E51D-FFC6D515F7E7}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -5127,7 +5123,7 @@
         <v>31</v>
       </c>
       <c r="J1" s="383" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="K1" s="383"/>
       <c r="L1" s="383"/>
@@ -5469,8 +5465,8 @@
       <c r="J21" s="172" t="s">
         <v>28</v>
       </c>
-      <c r="K21" s="488"/>
-      <c r="L21" s="489"/>
+      <c r="K21" s="487"/>
+      <c r="L21" s="488"/>
       <c r="M21" s="95"/>
       <c r="Q21" s="8" t="s">
         <v>220</v>
@@ -5489,8 +5485,8 @@
       <c r="J22" s="173" t="s">
         <v>68</v>
       </c>
-      <c r="K22" s="488"/>
-      <c r="L22" s="489"/>
+      <c r="K22" s="487"/>
+      <c r="L22" s="488"/>
       <c r="Q22" s="8" t="s">
         <v>219</v>
       </c>
@@ -5508,10 +5504,10 @@
       <c r="J23" s="171" t="s">
         <v>43</v>
       </c>
-      <c r="K23" s="490" t="s">
+      <c r="K23" s="489" t="s">
         <v>289</v>
       </c>
-      <c r="L23" s="491"/>
+      <c r="L23" s="490"/>
       <c r="M23" s="98"/>
     </row>
     <row r="24" spans="1:17" ht="14" thickBot="1" x14ac:dyDescent="0.2">
@@ -5722,27 +5718,13 @@
       <c r="G36" s="254"/>
       <c r="H36" s="101"/>
       <c r="I36" s="102"/>
-      <c r="J36" s="254" t="s">
-        <v>298</v>
-      </c>
-      <c r="K36" s="254">
-        <v>13</v>
-      </c>
-      <c r="L36" s="384">
-        <v>0.94251270562700806</v>
-      </c>
-      <c r="M36" s="254">
-        <v>33</v>
-      </c>
-      <c r="N36" s="254">
-        <v>5</v>
-      </c>
-      <c r="O36" s="254">
-        <v>4</v>
-      </c>
-      <c r="P36" s="254">
-        <v>3</v>
-      </c>
+      <c r="J36"/>
+      <c r="K36"/>
+      <c r="L36"/>
+      <c r="M36"/>
+      <c r="N36"/>
+      <c r="O36"/>
+      <c r="P36"/>
     </row>
     <row r="37" spans="1:16" ht="13" x14ac:dyDescent="0.15">
       <c r="A37" s="254"/>
@@ -5754,27 +5736,13 @@
       <c r="G37" s="254"/>
       <c r="H37" s="101"/>
       <c r="I37" s="102"/>
-      <c r="J37" s="254" t="s">
-        <v>298</v>
-      </c>
-      <c r="K37" s="254">
-        <v>13</v>
-      </c>
-      <c r="L37" s="384">
-        <v>0.94203420525371639</v>
-      </c>
-      <c r="M37" s="254">
-        <v>35</v>
-      </c>
-      <c r="N37" s="254">
-        <v>5</v>
-      </c>
-      <c r="O37" s="254">
-        <v>4</v>
-      </c>
-      <c r="P37" s="254">
-        <v>3</v>
-      </c>
+      <c r="J37"/>
+      <c r="K37"/>
+      <c r="L37"/>
+      <c r="M37"/>
+      <c r="N37"/>
+      <c r="O37"/>
+      <c r="P37"/>
     </row>
     <row r="38" spans="1:16" ht="13" x14ac:dyDescent="0.15">
       <c r="A38" s="254"/>
@@ -5786,27 +5754,13 @@
       <c r="G38" s="254"/>
       <c r="H38" s="101"/>
       <c r="I38" s="102"/>
-      <c r="J38" s="254" t="s">
-        <v>298</v>
-      </c>
-      <c r="K38" s="254">
-        <v>13</v>
-      </c>
-      <c r="L38" s="384">
-        <v>0.94222085795714505</v>
-      </c>
-      <c r="M38" s="254">
-        <v>38</v>
-      </c>
-      <c r="N38" s="254">
-        <v>5</v>
-      </c>
-      <c r="O38" s="254">
-        <v>4</v>
-      </c>
-      <c r="P38" s="254">
-        <v>3</v>
-      </c>
+      <c r="J38"/>
+      <c r="K38"/>
+      <c r="L38"/>
+      <c r="M38"/>
+      <c r="N38"/>
+      <c r="O38"/>
+      <c r="P38"/>
     </row>
     <row r="39" spans="1:16" ht="13" x14ac:dyDescent="0.15">
       <c r="A39" s="254"/>
@@ -5818,27 +5772,13 @@
       <c r="G39" s="254"/>
       <c r="H39" s="101"/>
       <c r="I39" s="102"/>
-      <c r="J39" s="254" t="s">
-        <v>298</v>
-      </c>
-      <c r="K39" s="254">
-        <v>13</v>
-      </c>
-      <c r="L39" s="384">
-        <v>0.94250250865293794</v>
-      </c>
-      <c r="M39" s="254">
-        <v>39</v>
-      </c>
-      <c r="N39" s="254">
-        <v>5</v>
-      </c>
-      <c r="O39" s="254">
-        <v>4</v>
-      </c>
-      <c r="P39" s="254">
-        <v>3</v>
-      </c>
+      <c r="J39"/>
+      <c r="K39"/>
+      <c r="L39"/>
+      <c r="M39"/>
+      <c r="N39"/>
+      <c r="O39"/>
+      <c r="P39"/>
     </row>
     <row r="40" spans="1:16" ht="13" x14ac:dyDescent="0.15">
       <c r="A40" s="254"/>
@@ -5850,27 +5790,13 @@
       <c r="G40" s="254"/>
       <c r="H40" s="101"/>
       <c r="I40" s="102"/>
-      <c r="J40" s="254" t="s">
-        <v>298</v>
-      </c>
-      <c r="K40" s="254">
-        <v>13</v>
-      </c>
-      <c r="L40" s="384">
-        <v>0.94163916617325527</v>
-      </c>
-      <c r="M40" s="254">
-        <v>209</v>
-      </c>
-      <c r="N40" s="254">
-        <v>27</v>
-      </c>
-      <c r="O40" s="254">
-        <v>19</v>
-      </c>
-      <c r="P40" s="254">
-        <v>2</v>
-      </c>
+      <c r="J40"/>
+      <c r="K40"/>
+      <c r="L40"/>
+      <c r="M40"/>
+      <c r="N40"/>
+      <c r="O40"/>
+      <c r="P40"/>
     </row>
     <row r="41" spans="1:16" ht="13" x14ac:dyDescent="0.15">
       <c r="A41" s="254"/>
@@ -5882,27 +5808,13 @@
       <c r="G41" s="254"/>
       <c r="H41" s="101"/>
       <c r="I41" s="102"/>
-      <c r="J41" s="254" t="s">
-        <v>298</v>
-      </c>
-      <c r="K41" s="254">
-        <v>13</v>
-      </c>
-      <c r="L41" s="384">
-        <v>0.94175123391988769</v>
-      </c>
-      <c r="M41" s="254">
-        <v>212</v>
-      </c>
-      <c r="N41" s="254">
-        <v>27</v>
-      </c>
-      <c r="O41" s="254">
-        <v>19</v>
-      </c>
-      <c r="P41" s="254">
-        <v>2</v>
-      </c>
+      <c r="J41"/>
+      <c r="K41"/>
+      <c r="L41"/>
+      <c r="M41"/>
+      <c r="N41"/>
+      <c r="O41"/>
+      <c r="P41"/>
     </row>
     <row r="42" spans="1:16" ht="13" x14ac:dyDescent="0.15">
       <c r="A42" s="254"/>
@@ -5914,27 +5826,13 @@
       <c r="G42" s="254"/>
       <c r="H42" s="101"/>
       <c r="I42" s="102"/>
-      <c r="J42" s="254" t="s">
-        <v>298</v>
-      </c>
-      <c r="K42" s="254">
-        <v>13</v>
-      </c>
-      <c r="L42" s="384">
-        <v>0.94241685035735934</v>
-      </c>
-      <c r="M42" s="254">
-        <v>214</v>
-      </c>
-      <c r="N42" s="254">
-        <v>27</v>
-      </c>
-      <c r="O42" s="254">
-        <v>19</v>
-      </c>
-      <c r="P42" s="254">
-        <v>2</v>
-      </c>
+      <c r="J42"/>
+      <c r="K42"/>
+      <c r="L42"/>
+      <c r="M42"/>
+      <c r="N42"/>
+      <c r="O42"/>
+      <c r="P42"/>
     </row>
     <row r="43" spans="1:16" ht="13" x14ac:dyDescent="0.15">
       <c r="A43" s="254"/>
@@ -5946,27 +5844,13 @@
       <c r="G43" s="254"/>
       <c r="H43" s="101"/>
       <c r="I43" s="102"/>
-      <c r="J43" s="254" t="s">
-        <v>298</v>
-      </c>
-      <c r="K43" s="254">
-        <v>13</v>
-      </c>
-      <c r="L43" s="384">
-        <v>0.9427863864551761</v>
-      </c>
-      <c r="M43" s="254">
-        <v>215</v>
-      </c>
-      <c r="N43" s="254">
-        <v>27</v>
-      </c>
-      <c r="O43" s="254">
-        <v>19</v>
-      </c>
-      <c r="P43" s="254">
-        <v>2</v>
-      </c>
+      <c r="J43"/>
+      <c r="K43"/>
+      <c r="L43"/>
+      <c r="M43"/>
+      <c r="N43"/>
+      <c r="O43"/>
+      <c r="P43"/>
     </row>
     <row r="44" spans="1:16" ht="13" x14ac:dyDescent="0.15">
       <c r="A44" s="254"/>
@@ -5978,6 +5862,13 @@
       <c r="G44" s="254"/>
       <c r="H44" s="101"/>
       <c r="I44" s="102"/>
+      <c r="J44"/>
+      <c r="K44"/>
+      <c r="L44"/>
+      <c r="M44"/>
+      <c r="N44"/>
+      <c r="O44"/>
+      <c r="P44"/>
     </row>
     <row r="45" spans="1:16" ht="13" x14ac:dyDescent="0.15">
       <c r="A45" s="254"/>
@@ -5989,12 +5880,13 @@
       <c r="G45" s="254"/>
       <c r="H45" s="101"/>
       <c r="I45" s="102"/>
-      <c r="J45" s="216" t="s">
-        <v>396</v>
-      </c>
-      <c r="K45" s="96"/>
-      <c r="L45" s="96"/>
-      <c r="M45" s="94"/>
+      <c r="J45"/>
+      <c r="K45"/>
+      <c r="L45"/>
+      <c r="M45"/>
+      <c r="N45"/>
+      <c r="O45"/>
+      <c r="P45"/>
     </row>
     <row r="46" spans="1:16" ht="13" x14ac:dyDescent="0.15">
       <c r="A46" s="254"/>
@@ -6006,27 +5898,13 @@
       <c r="G46" s="254"/>
       <c r="H46" s="101"/>
       <c r="I46" s="102"/>
-      <c r="J46" s="254" t="s">
-        <v>330</v>
-      </c>
-      <c r="K46" s="254">
-        <v>45</v>
-      </c>
-      <c r="L46" s="381">
-        <v>0.92135428336255676</v>
-      </c>
-      <c r="M46" s="254">
-        <v>178</v>
-      </c>
-      <c r="N46" s="254">
-        <v>23</v>
-      </c>
-      <c r="O46" s="254">
-        <v>16</v>
-      </c>
-      <c r="P46" s="254">
-        <v>3</v>
-      </c>
+      <c r="J46"/>
+      <c r="K46"/>
+      <c r="L46"/>
+      <c r="M46"/>
+      <c r="N46"/>
+      <c r="O46"/>
+      <c r="P46"/>
     </row>
     <row r="47" spans="1:16" ht="13" x14ac:dyDescent="0.15">
       <c r="A47" s="254"/>
@@ -6038,27 +5916,13 @@
       <c r="G47" s="254"/>
       <c r="H47" s="101"/>
       <c r="I47" s="102"/>
-      <c r="J47" s="254" t="s">
-        <v>330</v>
-      </c>
-      <c r="K47" s="254">
-        <v>45</v>
-      </c>
-      <c r="L47" s="381">
-        <v>0.95501807401487182</v>
-      </c>
-      <c r="M47" s="254">
-        <v>179</v>
-      </c>
-      <c r="N47" s="254">
-        <v>23</v>
-      </c>
-      <c r="O47" s="254">
-        <v>16</v>
-      </c>
-      <c r="P47" s="254">
-        <v>3</v>
-      </c>
+      <c r="J47"/>
+      <c r="K47"/>
+      <c r="L47"/>
+      <c r="M47"/>
+      <c r="N47"/>
+      <c r="O47"/>
+      <c r="P47"/>
     </row>
     <row r="48" spans="1:16" ht="13" x14ac:dyDescent="0.15">
       <c r="A48" s="254"/>
@@ -6070,27 +5934,13 @@
       <c r="G48" s="254"/>
       <c r="H48" s="101"/>
       <c r="I48" s="102"/>
-      <c r="J48" s="254" t="s">
-        <v>330</v>
-      </c>
-      <c r="K48" s="254">
-        <v>45</v>
-      </c>
-      <c r="L48" s="381">
-        <v>0.93934464884733304</v>
-      </c>
-      <c r="M48" s="254">
-        <v>182</v>
-      </c>
-      <c r="N48" s="254">
-        <v>23</v>
-      </c>
-      <c r="O48" s="254">
-        <v>16</v>
-      </c>
-      <c r="P48" s="254">
-        <v>3</v>
-      </c>
+      <c r="J48"/>
+      <c r="K48"/>
+      <c r="L48"/>
+      <c r="M48"/>
+      <c r="N48"/>
+      <c r="O48"/>
+      <c r="P48"/>
     </row>
     <row r="49" spans="1:16" ht="13" x14ac:dyDescent="0.15">
       <c r="A49" s="254"/>
@@ -6102,27 +5952,13 @@
       <c r="G49" s="254"/>
       <c r="H49" s="101"/>
       <c r="I49" s="102"/>
-      <c r="J49" s="254" t="s">
-        <v>330</v>
-      </c>
-      <c r="K49" s="254">
-        <v>45</v>
-      </c>
-      <c r="L49" s="381">
-        <v>0.95685362249056372</v>
-      </c>
-      <c r="M49" s="254">
-        <v>184</v>
-      </c>
-      <c r="N49" s="254">
-        <v>23</v>
-      </c>
-      <c r="O49" s="254">
-        <v>16</v>
-      </c>
-      <c r="P49" s="254">
-        <v>3</v>
-      </c>
+      <c r="J49"/>
+      <c r="K49"/>
+      <c r="L49"/>
+      <c r="M49"/>
+      <c r="N49"/>
+      <c r="O49"/>
+      <c r="P49"/>
     </row>
     <row r="50" spans="1:16" ht="13" x14ac:dyDescent="0.15">
       <c r="A50" s="254"/>
@@ -6134,6 +5970,13 @@
       <c r="G50" s="254"/>
       <c r="H50" s="101"/>
       <c r="I50" s="102"/>
+      <c r="J50"/>
+      <c r="K50"/>
+      <c r="L50"/>
+      <c r="M50"/>
+      <c r="N50"/>
+      <c r="O50"/>
+      <c r="P50"/>
     </row>
     <row r="51" spans="1:16" ht="13" x14ac:dyDescent="0.15">
       <c r="A51" s="254"/>
@@ -6145,6 +5988,13 @@
       <c r="G51" s="254"/>
       <c r="H51" s="101"/>
       <c r="I51" s="102"/>
+      <c r="J51"/>
+      <c r="K51"/>
+      <c r="L51"/>
+      <c r="M51"/>
+      <c r="N51"/>
+      <c r="O51"/>
+      <c r="P51"/>
     </row>
     <row r="52" spans="1:16" ht="13" x14ac:dyDescent="0.15">
       <c r="A52" s="254"/>
@@ -6156,10 +6006,13 @@
       <c r="G52" s="254"/>
       <c r="H52" s="101"/>
       <c r="I52" s="102"/>
-      <c r="J52" s="216"/>
-      <c r="K52" s="96"/>
-      <c r="L52" s="96"/>
-      <c r="M52" s="94"/>
+      <c r="J52"/>
+      <c r="K52"/>
+      <c r="L52"/>
+      <c r="M52"/>
+      <c r="N52"/>
+      <c r="O52"/>
+      <c r="P52"/>
     </row>
     <row r="53" spans="1:16" ht="13" x14ac:dyDescent="0.15">
       <c r="A53" s="254"/>
@@ -6171,6 +6024,13 @@
       <c r="G53" s="254"/>
       <c r="H53" s="101"/>
       <c r="I53" s="102"/>
+      <c r="J53"/>
+      <c r="K53"/>
+      <c r="L53"/>
+      <c r="M53"/>
+      <c r="N53"/>
+      <c r="O53"/>
+      <c r="P53"/>
     </row>
     <row r="54" spans="1:16" ht="13" x14ac:dyDescent="0.15">
       <c r="A54" s="254"/>
@@ -6182,10 +6042,13 @@
       <c r="G54" s="254"/>
       <c r="H54" s="101"/>
       <c r="I54" s="102"/>
-      <c r="J54" s="487">
-        <f>H54</f>
-        <v>0</v>
-      </c>
+      <c r="J54"/>
+      <c r="K54"/>
+      <c r="L54"/>
+      <c r="M54"/>
+      <c r="N54"/>
+      <c r="O54"/>
+      <c r="P54"/>
     </row>
     <row r="55" spans="1:16" ht="13" x14ac:dyDescent="0.15">
       <c r="A55" s="254"/>
@@ -6197,6 +6060,13 @@
       <c r="G55" s="254"/>
       <c r="H55" s="101"/>
       <c r="I55" s="102"/>
+      <c r="J55"/>
+      <c r="K55"/>
+      <c r="L55"/>
+      <c r="M55"/>
+      <c r="N55"/>
+      <c r="O55"/>
+      <c r="P55"/>
     </row>
     <row r="56" spans="1:16" ht="13" x14ac:dyDescent="0.15">
       <c r="A56" s="254"/>
@@ -21523,7 +21393,7 @@
       <c r="E27" s="254"/>
       <c r="F27" s="276"/>
       <c r="J27" s="216" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="U27" s="219"/>
       <c r="AB27">
@@ -21543,7 +21413,7 @@
       <c r="E28" s="254"/>
       <c r="F28" s="276"/>
       <c r="J28" s="254" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="K28" s="254">
         <v>4</v>
@@ -21575,7 +21445,7 @@
       <c r="E29" s="254"/>
       <c r="F29" s="276"/>
       <c r="J29" s="254" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="K29" s="254">
         <v>4</v>
@@ -27222,16 +27092,16 @@
         <v>8</v>
       </c>
       <c r="T3" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="U3">
         <v>10</v>
       </c>
       <c r="X3" t="s">
+        <v>397</v>
+      </c>
+      <c r="Y3" t="s">
         <v>398</v>
-      </c>
-      <c r="Y3" t="s">
-        <v>399</v>
       </c>
       <c r="Z3">
         <v>3.9383703924826614E-16</v>
@@ -27286,7 +27156,7 @@
         <v>8</v>
       </c>
       <c r="T4" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="U4">
         <v>12</v>
@@ -27295,7 +27165,7 @@
         <v>95</v>
       </c>
       <c r="Y4" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="Z4">
         <v>4.6053637111649585E-5</v>
@@ -27339,7 +27209,7 @@
         <v>8</v>
       </c>
       <c r="T5" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="U5">
         <v>12</v>
@@ -27348,7 +27218,7 @@
         <v>85</v>
       </c>
       <c r="Y5" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="Z5">
         <v>7.441076312253347E-6</v>
@@ -27392,7 +27262,7 @@
         <v>8</v>
       </c>
       <c r="T6" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="U6">
         <v>12</v>
@@ -27401,7 +27271,7 @@
         <v>10</v>
       </c>
       <c r="Y6" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="Z6">
         <v>6.8785803843513557E-15</v>
@@ -27448,7 +27318,7 @@
         <v>26</v>
       </c>
       <c r="Y7" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="Z7">
         <v>2.0831349061363922E-8</v>
@@ -27477,7 +27347,7 @@
         <v>8</v>
       </c>
       <c r="X8" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="Z8">
         <v>1.2651917051005516E-6</v>
@@ -27522,7 +27392,7 @@
         <v>31</v>
       </c>
       <c r="R11" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="S11">
         <v>8</v>
@@ -27530,7 +27400,7 @@
     </row>
     <row r="12" spans="1:32" ht="12" thickBot="1" x14ac:dyDescent="0.2">
       <c r="R12" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="S12">
         <v>8</v>
@@ -27556,7 +27426,7 @@
       <c r="M13" s="15"/>
       <c r="N13" s="26"/>
       <c r="R13" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="S13">
         <v>8</v>
@@ -27572,7 +27442,7 @@
       <c r="J14" s="2"/>
       <c r="N14" s="27"/>
       <c r="R14" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="S14">
         <v>8</v>
@@ -27582,7 +27452,7 @@
       <c r="A15" s="29"/>
       <c r="N15" s="27"/>
       <c r="R15" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="S15">
         <v>8</v>
@@ -27594,7 +27464,7 @@
       <c r="G16" s="2"/>
       <c r="N16" s="27"/>
       <c r="R16" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="S16">
         <v>8</v>
@@ -27616,7 +27486,7 @@
       <c r="M17" s="6"/>
       <c r="N17" s="27"/>
       <c r="R17" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="S17">
         <v>8</v>
@@ -27628,7 +27498,7 @@
       <c r="G18" s="1"/>
       <c r="N18" s="27"/>
       <c r="R18" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="S18">
         <v>8</v>
@@ -27638,7 +27508,7 @@
       <c r="A19" s="29"/>
       <c r="N19" s="27"/>
       <c r="R19" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="S19">
         <v>8</v>
@@ -27648,7 +27518,7 @@
       <c r="A20" s="29"/>
       <c r="N20" s="27"/>
       <c r="R20" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="S20">
         <v>8</v>
@@ -27670,7 +27540,7 @@
       <c r="M21" s="6"/>
       <c r="N21" s="27"/>
       <c r="R21" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="S21">
         <v>8</v>
@@ -27682,7 +27552,7 @@
       <c r="G22" s="1"/>
       <c r="N22" s="27"/>
       <c r="R22" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="S22">
         <v>8</v>
@@ -27700,7 +27570,7 @@
       <c r="G23" s="1"/>
       <c r="N23" s="27"/>
       <c r="R23" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="S23">
         <v>8</v>
@@ -27718,7 +27588,7 @@
       <c r="G24" s="1"/>
       <c r="N24" s="27"/>
       <c r="R24" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="S24">
         <v>8</v>
@@ -27737,7 +27607,7 @@
       <c r="G25" s="1"/>
       <c r="N25" s="27"/>
       <c r="R25" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="S25">
         <v>8</v>
@@ -27756,7 +27626,7 @@
       <c r="G26" s="1"/>
       <c r="N26" s="27"/>
       <c r="R26" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="S26">
         <v>8</v>
@@ -27783,7 +27653,7 @@
       <c r="M27" s="31"/>
       <c r="N27" s="32"/>
       <c r="R27" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="S27">
         <v>8</v>
@@ -27793,7 +27663,7 @@
       <c r="B28" s="1"/>
       <c r="G28" s="1"/>
       <c r="R28" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="S28">
         <v>8</v>
@@ -27803,7 +27673,7 @@
       <c r="B29" s="1"/>
       <c r="G29" s="1"/>
       <c r="R29" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="S29">
         <v>8</v>
@@ -27829,7 +27699,7 @@
       <c r="M30" s="15"/>
       <c r="N30" s="26"/>
       <c r="R30" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="S30">
         <v>8</v>
@@ -27841,7 +27711,7 @@
       <c r="G31" s="1"/>
       <c r="N31" s="27"/>
       <c r="R31" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="S31">
         <v>8</v>
@@ -27889,7 +27759,7 @@
         <v>96</v>
       </c>
       <c r="R32" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="S32">
         <v>8</v>
@@ -27949,7 +27819,7 @@
         <v>13</v>
       </c>
       <c r="R33" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="S33">
         <v>8</v>
@@ -28010,7 +27880,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="R34" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="S34">
         <v>8</v>
@@ -28071,7 +27941,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="R35" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="S35">
         <v>8</v>
@@ -28132,7 +28002,7 @@
         <v/>
       </c>
       <c r="R36" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="S36">
         <v>8</v>
@@ -28144,7 +28014,7 @@
       <c r="G37" s="1"/>
       <c r="N37" s="27"/>
       <c r="R37" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="S37">
         <v>8</v>
@@ -28192,7 +28062,7 @@
         <v>96</v>
       </c>
       <c r="R38" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="S38">
         <v>8</v>
@@ -28252,7 +28122,7 @@
         <v>26</v>
       </c>
       <c r="R39" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="S39">
         <v>8</v>
@@ -28313,7 +28183,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="R40" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="S40">
         <v>8</v>
@@ -28374,7 +28244,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="R41" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="S41">
         <v>8</v>
@@ -28435,7 +28305,7 @@
         <v/>
       </c>
       <c r="R42" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="S42">
         <v>8</v>
@@ -28447,7 +28317,7 @@
       <c r="G43" s="1"/>
       <c r="N43" s="27"/>
       <c r="R43" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="S43">
         <v>8</v>
@@ -28495,7 +28365,7 @@
         <v>96</v>
       </c>
       <c r="R44" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="S44">
         <v>8</v>
@@ -28555,7 +28425,7 @@
         <v>39</v>
       </c>
       <c r="R45" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="S45">
         <v>8</v>
@@ -28616,7 +28486,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="R46" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="S46">
         <v>8</v>
@@ -28677,7 +28547,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="R47" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="S47">
         <v>8</v>
@@ -28738,7 +28608,7 @@
         <v/>
       </c>
       <c r="R48" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="S48">
         <v>8</v>
@@ -28750,7 +28620,7 @@
       <c r="G49" s="1"/>
       <c r="N49" s="27"/>
       <c r="R49" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="S49">
         <v>8</v>
@@ -28798,7 +28668,7 @@
         <v>96</v>
       </c>
       <c r="R50" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="S50">
         <v>8</v>
@@ -28858,7 +28728,7 @@
         <v>52</v>
       </c>
       <c r="R51" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="S51">
         <v>8</v>
@@ -28919,7 +28789,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="R52" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="S52">
         <v>8</v>
@@ -28980,7 +28850,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="R53" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="S53">
         <v>8</v>
@@ -29041,7 +28911,7 @@
         <v/>
       </c>
       <c r="R54" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="S54">
         <v>8</v>
@@ -29052,7 +28922,7 @@
       <c r="G55" s="1"/>
       <c r="N55" s="27"/>
       <c r="R55" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="S55">
         <v>8</v>
@@ -29100,7 +28970,7 @@
         <v>96</v>
       </c>
       <c r="R56" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="S56">
         <v>8</v>
@@ -29160,7 +29030,7 @@
         <v>65</v>
       </c>
       <c r="R57" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="S57">
         <v>8</v>
@@ -29221,7 +29091,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="R58" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="S58">
         <v>8</v>
@@ -29282,7 +29152,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="R59" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="S59">
         <v>8</v>
@@ -29343,7 +29213,7 @@
         <v/>
       </c>
       <c r="R60" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="S60">
         <v>8</v>
@@ -29365,7 +29235,7 @@
       <c r="M61" s="6"/>
       <c r="N61" s="110"/>
       <c r="R61" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="S61">
         <v>8</v>
@@ -33102,12 +32972,12 @@
         <f>DGET($B$176:$H$182,"Type",$F$183:$F$184)</f>
         <v>#NUM!</v>
       </c>
-      <c r="G186" s="492">
+      <c r="G186" s="491">
         <f>MAX(AB3:AB8)</f>
         <v>0.84069036063391389</v>
       </c>
-      <c r="H186" s="493"/>
-      <c r="I186" s="493"/>
+      <c r="H186" s="492"/>
+      <c r="I186" s="492"/>
       <c r="J186" s="362" t="str">
         <f>LOOKUP($G$186,$AB$3:$AB$6,$X$3:$X$6)</f>
         <v>SampleID</v>
@@ -33560,7 +33430,7 @@
     </row>
     <row r="10" spans="1:23" ht="14" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="L10" s="191">
         <v>0.13258944002979564</v>
@@ -33617,13 +33487,13 @@
     </row>
     <row r="12" spans="1:23" ht="12" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A12" s="386" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B12" s="386"/>
-      <c r="R12" s="494" t="s">
+      <c r="R12" s="493" t="s">
         <v>122</v>
       </c>
-      <c r="S12" s="494"/>
+      <c r="S12" s="493"/>
       <c r="T12" s="251">
         <f>L1</f>
         <v>1</v>
@@ -33637,15 +33507,15 @@
     </row>
     <row r="13" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A13" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B13">
         <v>0.99998209662836235</v>
       </c>
-      <c r="R13" s="494" t="s">
+      <c r="R13" s="493" t="s">
         <v>138</v>
       </c>
-      <c r="S13" s="494"/>
+      <c r="S13" s="493"/>
       <c r="T13" s="251" t="str">
         <f>IF(ISERROR('Past LS'!M25),"",'Past LS'!M25)</f>
         <v/>
@@ -33658,15 +33528,15 @@
     </row>
     <row r="14" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A14" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B14">
         <v>0.99996419357725541</v>
       </c>
-      <c r="R14" s="494" t="s">
+      <c r="R14" s="493" t="s">
         <v>138</v>
       </c>
-      <c r="S14" s="494"/>
+      <c r="S14" s="493"/>
       <c r="T14" s="252" t="str">
         <f>IF(ISERROR('Past LS'!N25),"",'Past LS'!N25)</f>
         <v/>
@@ -33678,15 +33548,15 @@
     </row>
     <row r="15" spans="1:23" ht="12" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B15">
         <v>0.99996337979492023</v>
       </c>
-      <c r="R15" s="494" t="s">
+      <c r="R15" s="493" t="s">
         <v>138</v>
       </c>
-      <c r="S15" s="494"/>
+      <c r="S15" s="493"/>
       <c r="T15" s="253" t="str">
         <f>IF(ISERROR('Past LS'!O25),"",'Past LS'!O25)</f>
         <v/>
@@ -33698,35 +33568,35 @@
     </row>
     <row r="16" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A16" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B16">
         <v>2.2060793350162878E-3</v>
       </c>
-      <c r="R16" s="494"/>
-      <c r="S16" s="494"/>
+      <c r="R16" s="493"/>
+      <c r="S16" s="493"/>
     </row>
     <row r="17" spans="1:25" ht="12" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A17" s="31" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B17" s="31">
         <v>46</v>
       </c>
-      <c r="R17" s="494" t="s">
+      <c r="R17" s="493" t="s">
         <v>238</v>
       </c>
-      <c r="S17" s="494"/>
+      <c r="S17" s="493"/>
       <c r="T17">
         <f>COUNT(T2:T11)</f>
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:25" x14ac:dyDescent="0.15">
-      <c r="R18" s="494" t="s">
+      <c r="R18" s="493" t="s">
         <v>134</v>
       </c>
-      <c r="S18" s="494"/>
+      <c r="S18" s="493"/>
       <c r="T18">
         <f>COUNT(T12:T15)</f>
         <v>1</v>
@@ -33734,30 +33604,30 @@
     </row>
     <row r="19" spans="1:25" ht="12" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="20" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A20" s="385"/>
       <c r="B20" s="385" t="s">
+        <v>366</v>
+      </c>
+      <c r="C20" s="385" t="s">
         <v>367</v>
       </c>
-      <c r="C20" s="385" t="s">
+      <c r="D20" s="385" t="s">
         <v>368</v>
       </c>
-      <c r="D20" s="385" t="s">
+      <c r="E20" s="385" t="s">
         <v>369</v>
       </c>
-      <c r="E20" s="385" t="s">
+      <c r="F20" s="385" t="s">
         <v>370</v>
-      </c>
-      <c r="F20" s="385" t="s">
-        <v>371</v>
       </c>
     </row>
     <row r="21" spans="1:25" ht="12" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B21">
         <v>1</v>
@@ -33777,7 +33647,7 @@
     </row>
     <row r="22" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A22" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B22">
         <v>44</v>
@@ -33790,7 +33660,7 @@
       </c>
       <c r="S22" s="264"/>
       <c r="T22" s="113" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="U22" s="113"/>
       <c r="V22" s="113"/>
@@ -33802,7 +33672,7 @@
     </row>
     <row r="23" spans="1:25" ht="12" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A23" s="31" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B23" s="31">
         <v>45</v>
@@ -33841,28 +33711,28 @@
     <row r="25" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A25" s="385"/>
       <c r="B25" s="385" t="s">
+        <v>371</v>
+      </c>
+      <c r="C25" s="385" t="s">
+        <v>359</v>
+      </c>
+      <c r="D25" s="385" t="s">
         <v>372</v>
       </c>
-      <c r="C25" s="385" t="s">
-        <v>360</v>
-      </c>
-      <c r="D25" s="385" t="s">
+      <c r="E25" s="385" t="s">
         <v>373</v>
       </c>
-      <c r="E25" s="385" t="s">
+      <c r="F25" s="385" t="s">
         <v>374</v>
       </c>
-      <c r="F25" s="385" t="s">
+      <c r="G25" s="385" t="s">
         <v>375</v>
       </c>
-      <c r="G25" s="385" t="s">
+      <c r="H25" s="385" t="s">
         <v>376</v>
       </c>
-      <c r="H25" s="385" t="s">
+      <c r="I25" s="385" t="s">
         <v>377</v>
-      </c>
-      <c r="I25" s="385" t="s">
-        <v>378</v>
       </c>
       <c r="S25" s="265"/>
       <c r="T25" s="116" t="s">
@@ -33879,7 +33749,7 @@
     </row>
     <row r="26" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A26" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B26">
         <v>-2.6281921754625515E-2</v>
@@ -33918,7 +33788,7 @@
     </row>
     <row r="27" spans="1:25" ht="12" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A27" s="31" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B27" s="31">
         <v>0.19962526494789587</v>
@@ -33946,7 +33816,7 @@
       </c>
       <c r="S27" s="265"/>
       <c r="T27" s="116" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="U27" s="116"/>
       <c r="V27" s="116">
@@ -33966,19 +33836,19 @@
     <row r="29" spans="1:25" x14ac:dyDescent="0.15">
       <c r="S29" s="265"/>
       <c r="T29" s="116" t="s">
+        <v>385</v>
+      </c>
+      <c r="U29" s="116" t="s">
         <v>386</v>
       </c>
-      <c r="U29" s="116" t="s">
+      <c r="V29" s="156" t="s">
         <v>387</v>
       </c>
-      <c r="V29" s="156" t="s">
+      <c r="W29" s="116" t="s">
         <v>388</v>
       </c>
-      <c r="W29" s="116" t="s">
+      <c r="X29" s="117" t="s">
         <v>389</v>
-      </c>
-      <c r="X29" s="117" t="s">
-        <v>390</v>
       </c>
     </row>
     <row r="30" spans="1:25" x14ac:dyDescent="0.15">
@@ -33996,12 +33866,12 @@
         <v>4.0154655015724279</v>
       </c>
       <c r="X30" s="117" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="31" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A31" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="S31" s="266"/>
       <c r="T31" s="165">
@@ -34017,7 +33887,7 @@
         <v>4.9564022393490674</v>
       </c>
       <c r="X31" s="117" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="32" spans="1:25" ht="12" thickBot="1" x14ac:dyDescent="0.2">
@@ -34035,18 +33905,18 @@
         <v>6.0347031261822259</v>
       </c>
       <c r="X32" s="117" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="33" spans="1:24" x14ac:dyDescent="0.15">
       <c r="A33" s="385" t="s">
+        <v>380</v>
+      </c>
+      <c r="B33" s="385" t="s">
         <v>381</v>
       </c>
-      <c r="B33" s="385" t="s">
+      <c r="C33" s="385" t="s">
         <v>382</v>
-      </c>
-      <c r="C33" s="385" t="s">
-        <v>383</v>
       </c>
       <c r="S33" s="266"/>
       <c r="T33" s="165">
@@ -34062,7 +33932,7 @@
         <v>9.0177939443627988</v>
       </c>
       <c r="X33" s="117" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="34" spans="1:24" x14ac:dyDescent="0.15">
@@ -34098,16 +33968,16 @@
       </c>
       <c r="S35" s="266"/>
       <c r="T35" s="165" t="s">
+        <v>391</v>
+      </c>
+      <c r="U35" s="165" t="s">
         <v>392</v>
       </c>
-      <c r="U35" s="165" t="s">
+      <c r="V35" s="165" t="s">
         <v>393</v>
       </c>
-      <c r="V35" s="165" t="s">
+      <c r="W35" s="165" t="s">
         <v>394</v>
-      </c>
-      <c r="W35" s="165" t="s">
-        <v>395</v>
       </c>
       <c r="X35" s="117"/>
     </row>
@@ -35469,7 +35339,7 @@
         <v>264</v>
       </c>
       <c r="B44" s="344" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C44" s="429"/>
       <c r="AD44"/>
@@ -35480,17 +35350,17 @@
         <f>B50/B49</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="M45" s="495" t="s">
+      <c r="M45" s="494" t="s">
         <v>265</v>
       </c>
-      <c r="N45" s="496"/>
-      <c r="O45" s="496"/>
-      <c r="P45" s="496"/>
-      <c r="Q45" s="496"/>
-      <c r="R45" s="496"/>
-      <c r="S45" s="496"/>
-      <c r="T45" s="496"/>
-      <c r="U45" s="497"/>
+      <c r="N45" s="495"/>
+      <c r="O45" s="495"/>
+      <c r="P45" s="495"/>
+      <c r="Q45" s="495"/>
+      <c r="R45" s="495"/>
+      <c r="S45" s="495"/>
+      <c r="T45" s="495"/>
+      <c r="U45" s="496"/>
       <c r="AD45"/>
       <c r="AE45"/>
     </row>
@@ -35719,10 +35589,10 @@
         <v>6</v>
       </c>
       <c r="G50" s="259" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H50" s="259" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="I50" s="427" t="str">
         <f>IF(ISNUMBER(G50),$B$52*H50,"")</f>
@@ -35779,10 +35649,10 @@
         <v>7</v>
       </c>
       <c r="G51" s="444" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H51" s="444" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="I51" s="427" t="str">
         <f>IF(ISNUMBER(G51),$B$52*H51,"")</f>
@@ -35942,7 +35812,7 @@
       <c r="H54" s="259"/>
       <c r="I54" s="259"/>
       <c r="J54" s="453" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="K54" s="222"/>
       <c r="M54" s="392"/>
@@ -35990,10 +35860,10 @@
       <c r="G55" s="257"/>
       <c r="H55" s="259"/>
       <c r="I55" s="259" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="J55" s="453" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="K55" s="222"/>
       <c r="M55" s="405"/>
@@ -36039,16 +35909,16 @@
         <v>6</v>
       </c>
       <c r="G56" s="257" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H56" s="259" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="I56" s="259" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="J56" s="453" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="K56" s="222"/>
       <c r="M56" s="392"/>
@@ -36095,16 +35965,16 @@
         <v>7</v>
       </c>
       <c r="G57" s="258" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H57" s="260" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="I57" s="260" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="J57" s="454" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="K57" s="221"/>
       <c r="M57" s="392"/>
@@ -36441,16 +36311,16 @@
         <v>5</v>
       </c>
       <c r="B64" s="259" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C64" s="468" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="D64" s="468" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="E64" s="468" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="F64" s="467" t="str">
         <f t="shared" si="6"/>
@@ -36502,16 +36372,16 @@
         <v>6</v>
       </c>
       <c r="B65" s="259" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C65" s="468" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="D65" s="468" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="E65" s="468" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="F65" s="467" t="str">
         <f t="shared" si="6"/>
@@ -36563,16 +36433,16 @@
         <v>7</v>
       </c>
       <c r="B66" s="259" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C66" s="468" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="D66" s="468" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="E66" s="468" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="F66" s="467" t="str">
         <f t="shared" si="6"/>
@@ -36624,16 +36494,16 @@
         <v>8</v>
       </c>
       <c r="B67" s="259" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C67" s="468" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="D67" s="468" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="E67" s="468" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="F67" s="467" t="str">
         <f t="shared" si="6"/>
@@ -36685,16 +36555,16 @@
         <v>9</v>
       </c>
       <c r="B68" s="259" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C68" s="468" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="D68" s="468" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="E68" s="468" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="F68" s="467" t="str">
         <f t="shared" si="6"/>
@@ -36746,16 +36616,16 @@
         <v>10</v>
       </c>
       <c r="B69" s="260" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C69" s="469" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="D69" s="469" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="E69" s="469" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="F69" s="470" t="str">
         <f t="shared" si="6"/>
@@ -37126,19 +36996,19 @@
     </row>
     <row r="77" spans="1:31" ht="13" x14ac:dyDescent="0.15">
       <c r="A77" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B77" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C77" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="D77" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="E77" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="G77" s="224"/>
       <c r="H77" s="224"/>
@@ -37173,19 +37043,19 @@
     </row>
     <row r="78" spans="1:31" ht="14" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B78" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C78" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="D78" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="E78" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="G78" s="224"/>
       <c r="H78" s="224"/>
@@ -37231,12 +37101,12 @@
         <v>44</v>
       </c>
       <c r="E79" t="s">
-        <v>397</v>
-      </c>
-      <c r="G79" s="498" t="s">
+        <v>396</v>
+      </c>
+      <c r="G79" s="497" t="s">
         <v>268</v>
       </c>
-      <c r="H79" s="499"/>
+      <c r="H79" s="498"/>
       <c r="M79" s="392"/>
       <c r="N79" s="401"/>
       <c r="O79" s="403"/>
@@ -37270,7 +37140,7 @@
       <c r="C80" s="393"/>
       <c r="D80" s="426"/>
       <c r="E80" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="G80" s="355" t="s">
         <v>44</v>
@@ -37309,7 +37179,7 @@
       <c r="C81" s="477"/>
       <c r="D81" s="478"/>
       <c r="E81" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="G81" s="355" t="s">
         <v>269</v>
@@ -37348,7 +37218,7 @@
       <c r="C82" s="477"/>
       <c r="D82" s="478"/>
       <c r="E82" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="G82" s="355" t="s">
         <v>270</v>
@@ -37387,7 +37257,7 @@
       <c r="C83" s="477"/>
       <c r="D83" s="478"/>
       <c r="E83" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="G83" s="355" t="s">
         <v>271</v>
@@ -37422,19 +37292,19 @@
     </row>
     <row r="84" spans="1:31" ht="13" x14ac:dyDescent="0.15">
       <c r="A84" s="269" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B84" s="270" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C84" s="271" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="D84" s="352" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="E84" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="G84" s="355" t="s">
         <v>272</v>
@@ -37469,19 +37339,19 @@
     </row>
     <row r="85" spans="1:31" ht="14" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A85" s="269" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B85" s="270" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C85" s="271" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="D85" s="352" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="E85" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="G85" s="357" t="s">
         <v>273</v>
@@ -37516,19 +37386,19 @@
     </row>
     <row r="86" spans="1:31" ht="13" x14ac:dyDescent="0.15">
       <c r="A86" s="269" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B86" s="270" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C86" s="271" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="D86" s="352" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="E86" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="G86" s="86"/>
       <c r="M86" s="392"/>
@@ -37560,17 +37430,17 @@
     </row>
     <row r="87" spans="1:31" ht="13" x14ac:dyDescent="0.15">
       <c r="A87" s="269" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B87" s="270"/>
       <c r="C87" s="271" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="D87" s="352" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="E87" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="G87" s="86"/>
       <c r="M87" s="392"/>
@@ -37602,19 +37472,19 @@
     </row>
     <row r="88" spans="1:31" ht="13" x14ac:dyDescent="0.15">
       <c r="A88" s="269" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B88" s="270" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C88" s="271" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="D88" s="352" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="E88" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="M88" s="392"/>
       <c r="N88" s="401"/>
@@ -37645,19 +37515,19 @@
     </row>
     <row r="89" spans="1:31" ht="13" x14ac:dyDescent="0.15">
       <c r="A89" s="269" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B89" s="270" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C89" s="271" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="D89" s="352" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="E89" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="M89" s="405"/>
       <c r="N89" s="406"/>
@@ -37688,19 +37558,19 @@
     </row>
     <row r="90" spans="1:31" ht="13" x14ac:dyDescent="0.15">
       <c r="A90" s="269" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B90" s="270" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C90" s="271" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="D90" s="352" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="E90" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="M90" s="392"/>
       <c r="N90" s="401"/>
@@ -37731,19 +37601,19 @@
     </row>
     <row r="91" spans="1:31" ht="13" x14ac:dyDescent="0.15">
       <c r="A91" s="269" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B91" s="270" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C91" s="271" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="D91" s="352" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="E91" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="M91" s="392"/>
       <c r="N91" s="401"/>
@@ -37774,19 +37644,19 @@
     </row>
     <row r="92" spans="1:31" ht="13" x14ac:dyDescent="0.15">
       <c r="A92" s="269" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B92" s="313" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C92" s="271" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="D92" s="352" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="E92" s="314" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="M92" s="392"/>
       <c r="N92" s="401"/>
@@ -37817,19 +37687,19 @@
     </row>
     <row r="93" spans="1:31" ht="13" x14ac:dyDescent="0.15">
       <c r="A93" s="269" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B93" s="313" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C93" s="271" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="D93" s="352" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="E93" s="314" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="M93" s="392"/>
       <c r="N93" s="401"/>
@@ -37860,19 +37730,19 @@
     </row>
     <row r="94" spans="1:31" ht="13" x14ac:dyDescent="0.15">
       <c r="A94" s="269" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B94" s="313" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C94" s="271" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="D94" s="352" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="E94" s="314" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="M94" s="405"/>
       <c r="N94" s="406"/>
@@ -37903,19 +37773,19 @@
     </row>
     <row r="95" spans="1:31" ht="13" x14ac:dyDescent="0.15">
       <c r="A95" s="269" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B95" s="313" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C95" s="271" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="D95" s="352" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="E95" s="314" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="M95" s="392"/>
       <c r="N95" s="401"/>
@@ -37946,19 +37816,19 @@
     </row>
     <row r="96" spans="1:31" ht="13" x14ac:dyDescent="0.15">
       <c r="A96" s="269" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B96" s="313" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C96" s="271" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="D96" s="352" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="E96" s="314" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="M96" s="410"/>
       <c r="N96" s="411"/>
@@ -37989,19 +37859,19 @@
     </row>
     <row r="97" spans="1:31" ht="13" x14ac:dyDescent="0.15">
       <c r="A97" s="269" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B97" s="313" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C97" s="271" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="D97" s="352" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="E97" s="314" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="M97" s="392"/>
       <c r="N97" s="401"/>
@@ -38032,19 +37902,19 @@
     </row>
     <row r="98" spans="1:31" ht="13" x14ac:dyDescent="0.15">
       <c r="A98" s="269" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B98" s="313" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C98" s="271" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="D98" s="352" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="E98" s="314" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="M98" s="392"/>
       <c r="N98" s="401"/>
@@ -38075,19 +37945,19 @@
     </row>
     <row r="99" spans="1:31" ht="13" x14ac:dyDescent="0.15">
       <c r="A99" s="269" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B99" s="313" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C99" s="271" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="D99" s="352" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="E99" s="314" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="M99" s="392"/>
       <c r="N99" s="401"/>
@@ -38118,19 +37988,19 @@
     </row>
     <row r="100" spans="1:31" ht="13" x14ac:dyDescent="0.15">
       <c r="A100" s="269" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B100" s="313" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C100" s="271" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="D100" s="352" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="E100" s="314" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="M100" s="392"/>
       <c r="N100" s="401"/>
@@ -38364,16 +38234,16 @@
       <c r="D107" s="273"/>
       <c r="E107" s="314"/>
       <c r="M107" s="220" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="N107" s="223" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="O107" s="256" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="P107" s="223" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Q107" s="404" t="e">
         <f t="shared" si="0"/>
@@ -38405,16 +38275,16 @@
       <c r="D108" s="273"/>
       <c r="E108" s="314"/>
       <c r="M108" s="220" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="N108" s="223" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="O108" s="256" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="P108" s="223" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Q108" s="404" t="e">
         <f t="shared" si="0"/>
@@ -38446,16 +38316,16 @@
       <c r="D109" s="351"/>
       <c r="E109" s="314"/>
       <c r="M109" s="220" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="N109" s="223" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="O109" s="256" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="P109" s="223" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Q109" s="404" t="e">
         <f t="shared" si="0"/>
@@ -38487,16 +38357,16 @@
       <c r="D110" s="273"/>
       <c r="E110" s="314"/>
       <c r="M110" s="220" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="N110" s="223" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="O110" s="256" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="P110" s="223" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Q110" s="404" t="e">
         <f t="shared" si="0"/>
@@ -38528,16 +38398,16 @@
       <c r="D111" s="273"/>
       <c r="E111" s="314"/>
       <c r="M111" s="220" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="N111" s="223" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="O111" s="256" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="P111" s="223" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Q111" s="404" t="e">
         <f t="shared" si="0"/>
@@ -38569,16 +38439,16 @@
       <c r="D112" s="273"/>
       <c r="E112" s="314"/>
       <c r="M112" s="220" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="N112" s="223" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="O112" s="256" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="P112" s="223" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Q112" s="404" t="e">
         <f t="shared" si="0"/>
@@ -38610,16 +38480,16 @@
       <c r="D113" s="273"/>
       <c r="E113" s="314"/>
       <c r="M113" s="220" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="N113" s="223" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="O113" s="256" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="P113" s="223" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Q113" s="404" t="e">
         <f t="shared" ref="Q113:Q176" si="9">P113/O113</f>
@@ -38651,16 +38521,16 @@
       <c r="D114" s="273"/>
       <c r="E114" s="314"/>
       <c r="M114" s="220" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="N114" s="223" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="O114" s="256" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="P114" s="223" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Q114" s="404" t="e">
         <f t="shared" si="9"/>
@@ -38692,16 +38562,16 @@
       <c r="D115" s="273"/>
       <c r="E115" s="314"/>
       <c r="M115" s="220" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="N115" s="223" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="O115" s="256" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="P115" s="223" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Q115" s="404" t="e">
         <f t="shared" si="9"/>
@@ -38733,16 +38603,16 @@
       <c r="D116" s="273"/>
       <c r="E116" s="314"/>
       <c r="M116" s="206" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="N116" s="259" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="O116" s="257" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="P116" s="259" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Q116" s="404" t="e">
         <f t="shared" si="9"/>
@@ -38774,16 +38644,16 @@
       <c r="D117" s="273"/>
       <c r="E117" s="314"/>
       <c r="M117" s="206" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="N117" s="259" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="O117" s="257" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="P117" s="259" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Q117" s="404" t="e">
         <f t="shared" si="9"/>
@@ -38815,16 +38685,16 @@
       <c r="D118" s="273"/>
       <c r="E118" s="314"/>
       <c r="M118" s="206" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="N118" s="259" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="O118" s="257" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="P118" s="259" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Q118" s="404" t="e">
         <f t="shared" si="9"/>
@@ -38856,16 +38726,16 @@
       <c r="D119" s="273"/>
       <c r="E119" s="314"/>
       <c r="M119" s="206" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="N119" s="259" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="O119" s="257" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="P119" s="259" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Q119" s="404" t="e">
         <f t="shared" si="9"/>
@@ -38897,16 +38767,16 @@
       <c r="D120" s="273"/>
       <c r="E120" s="314"/>
       <c r="M120" s="206" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="N120" s="259" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="O120" s="257" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="P120" s="259" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Q120" s="404" t="e">
         <f t="shared" si="9"/>
@@ -38938,16 +38808,16 @@
       <c r="D121" s="273"/>
       <c r="E121" s="314"/>
       <c r="M121" s="206" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="N121" s="259" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="O121" s="257" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="P121" s="259" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Q121" s="404" t="e">
         <f t="shared" si="9"/>
@@ -38979,16 +38849,16 @@
       <c r="D122" s="273"/>
       <c r="E122" s="314"/>
       <c r="M122" s="206" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="N122" s="259" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="O122" s="257" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="P122" s="259" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Q122" s="404" t="e">
         <f t="shared" si="9"/>
@@ -39020,16 +38890,16 @@
       <c r="D123" s="273"/>
       <c r="E123" s="314"/>
       <c r="M123" s="206" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="N123" s="259" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="O123" s="257" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="P123" s="259" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Q123" s="404" t="e">
         <f t="shared" si="9"/>
@@ -39060,16 +38930,16 @@
       <c r="C124" s="271"/>
       <c r="D124" s="273"/>
       <c r="M124" s="206" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="N124" s="259" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="O124" s="257" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="P124" s="259" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Q124" s="404" t="e">
         <f t="shared" si="9"/>
@@ -39100,16 +38970,16 @@
       <c r="C125" s="271"/>
       <c r="D125" s="273"/>
       <c r="M125" s="206" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="N125" s="259" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="O125" s="257" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="P125" s="259" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Q125" s="404" t="e">
         <f t="shared" si="9"/>
@@ -39140,16 +39010,16 @@
       <c r="C126" s="271"/>
       <c r="D126" s="273"/>
       <c r="M126" s="206" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="N126" s="259" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="O126" s="257" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="P126" s="259" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Q126" s="404" t="e">
         <f t="shared" si="9"/>
@@ -39180,16 +39050,16 @@
       <c r="C127" s="271"/>
       <c r="D127" s="273"/>
       <c r="M127" s="206" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="N127" s="259" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="O127" s="257" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="P127" s="259" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Q127" s="404" t="e">
         <f t="shared" si="9"/>
@@ -39220,16 +39090,16 @@
       <c r="C128" s="271"/>
       <c r="D128" s="273"/>
       <c r="M128" s="206" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="N128" s="259" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="O128" s="257" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="P128" s="259" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Q128" s="404" t="e">
         <f t="shared" si="9"/>
@@ -39260,16 +39130,16 @@
       <c r="C129" s="271"/>
       <c r="D129" s="273"/>
       <c r="M129" s="206" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="N129" s="259" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="O129" s="257" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="P129" s="259" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Q129" s="404" t="e">
         <f t="shared" si="9"/>
@@ -39300,16 +39170,16 @@
       <c r="C130" s="271"/>
       <c r="D130" s="273"/>
       <c r="M130" s="206" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="N130" s="259" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="O130" s="257" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="P130" s="259" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Q130" s="404" t="e">
         <f t="shared" si="9"/>
@@ -39340,16 +39210,16 @@
       <c r="C131" s="271"/>
       <c r="D131" s="273"/>
       <c r="M131" s="206" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="N131" s="259" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="O131" s="257" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="P131" s="259" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Q131" s="404" t="e">
         <f t="shared" si="9"/>
@@ -39380,16 +39250,16 @@
       <c r="C132" s="271"/>
       <c r="D132" s="273"/>
       <c r="M132" s="206" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="N132" s="259" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="O132" s="257" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="P132" s="259" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Q132" s="404" t="e">
         <f t="shared" si="9"/>
@@ -39420,16 +39290,16 @@
       <c r="C133" s="271"/>
       <c r="D133" s="273"/>
       <c r="M133" s="206" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="N133" s="259" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="O133" s="257" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="P133" s="259" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Q133" s="404" t="e">
         <f t="shared" si="9"/>
@@ -39460,16 +39330,16 @@
       <c r="C134" s="271"/>
       <c r="D134" s="273"/>
       <c r="M134" s="206" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="N134" s="259" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="O134" s="257" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="P134" s="259" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Q134" s="404" t="e">
         <f t="shared" si="9"/>
@@ -39500,16 +39370,16 @@
       <c r="C135" s="271"/>
       <c r="D135" s="273"/>
       <c r="M135" s="206" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="N135" s="259" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="O135" s="257" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="P135" s="259" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Q135" s="404" t="e">
         <f t="shared" si="9"/>
@@ -39540,16 +39410,16 @@
       <c r="C136" s="271"/>
       <c r="D136" s="273"/>
       <c r="M136" s="206" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="N136" s="259" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="O136" s="257" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="P136" s="259" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Q136" s="404" t="e">
         <f t="shared" si="9"/>
@@ -39580,16 +39450,16 @@
       <c r="C137" s="271"/>
       <c r="D137" s="273"/>
       <c r="M137" s="206" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="N137" s="259" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="O137" s="257" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="P137" s="259" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Q137" s="404" t="e">
         <f t="shared" si="9"/>
@@ -39620,16 +39490,16 @@
       <c r="C138" s="271"/>
       <c r="D138" s="273"/>
       <c r="M138" s="206" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="N138" s="259" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="O138" s="257" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="P138" s="259" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Q138" s="404" t="e">
         <f t="shared" si="9"/>
@@ -39660,16 +39530,16 @@
       <c r="C139" s="271"/>
       <c r="D139" s="273"/>
       <c r="M139" s="206" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="N139" s="259" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="O139" s="257" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="P139" s="259" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Q139" s="404" t="e">
         <f t="shared" si="9"/>
@@ -39700,16 +39570,16 @@
       <c r="C140" s="271"/>
       <c r="D140" s="273"/>
       <c r="M140" s="206" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="N140" s="259" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="O140" s="257" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="P140" s="259" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Q140" s="404" t="e">
         <f t="shared" si="9"/>
@@ -39740,16 +39610,16 @@
       <c r="C141" s="271"/>
       <c r="D141" s="273"/>
       <c r="M141" s="206" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="N141" s="259" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="O141" s="257" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="P141" s="259" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Q141" s="404" t="e">
         <f t="shared" si="9"/>
@@ -39780,16 +39650,16 @@
       <c r="C142" s="271"/>
       <c r="D142" s="273"/>
       <c r="M142" s="206" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="N142" s="259" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="O142" s="257" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="P142" s="259" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Q142" s="404" t="e">
         <f t="shared" si="9"/>
@@ -39819,16 +39689,16 @@
       <c r="C143" s="271"/>
       <c r="D143" s="272"/>
       <c r="M143" s="206" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="N143" s="259" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="O143" s="257" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="P143" s="259" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Q143" s="404" t="e">
         <f t="shared" si="9"/>
@@ -39858,16 +39728,16 @@
       <c r="C144" s="271"/>
       <c r="D144" s="272"/>
       <c r="M144" s="206" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="N144" s="259" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="O144" s="257" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="P144" s="259" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Q144" s="404" t="e">
         <f t="shared" si="9"/>
@@ -39897,16 +39767,16 @@
       <c r="C145" s="271"/>
       <c r="D145" s="272"/>
       <c r="M145" s="206" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="N145" s="259" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="O145" s="257" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="P145" s="259" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Q145" s="404" t="e">
         <f t="shared" si="9"/>
@@ -39936,16 +39806,16 @@
       <c r="C146" s="271"/>
       <c r="D146" s="272"/>
       <c r="M146" s="206" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="N146" s="259" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="O146" s="257" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="P146" s="259" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Q146" s="404" t="e">
         <f t="shared" si="9"/>
@@ -39975,16 +39845,16 @@
       <c r="C147" s="271"/>
       <c r="D147" s="272"/>
       <c r="M147" s="206" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="N147" s="259" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="O147" s="257" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="P147" s="259" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Q147" s="404" t="e">
         <f t="shared" si="9"/>
@@ -40014,16 +39884,16 @@
       <c r="C148" s="271"/>
       <c r="D148" s="272"/>
       <c r="M148" s="206" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="N148" s="259" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="O148" s="257" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="P148" s="259" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Q148" s="404" t="e">
         <f t="shared" si="9"/>
@@ -40053,16 +39923,16 @@
       <c r="C149" s="271"/>
       <c r="D149" s="272"/>
       <c r="M149" s="206" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="N149" s="259" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="O149" s="257" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="P149" s="259" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Q149" s="404" t="e">
         <f t="shared" si="9"/>
@@ -40092,16 +39962,16 @@
       <c r="C150" s="271"/>
       <c r="D150" s="272"/>
       <c r="M150" s="206" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="N150" s="259" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="O150" s="257" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="P150" s="259" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Q150" s="404" t="e">
         <f t="shared" si="9"/>
@@ -40131,16 +40001,16 @@
       <c r="C151" s="271"/>
       <c r="D151" s="272"/>
       <c r="M151" s="206" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="N151" s="259" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="O151" s="257" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="P151" s="259" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Q151" s="404" t="e">
         <f t="shared" si="9"/>
@@ -40170,16 +40040,16 @@
       <c r="C152" s="271"/>
       <c r="D152" s="272"/>
       <c r="M152" s="206" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="N152" s="259" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="O152" s="257" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="P152" s="259" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Q152" s="404" t="e">
         <f t="shared" si="9"/>
@@ -40209,16 +40079,16 @@
       <c r="C153" s="271"/>
       <c r="D153" s="272"/>
       <c r="M153" s="206" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="N153" s="259" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="O153" s="257" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="P153" s="259" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Q153" s="404" t="e">
         <f t="shared" si="9"/>
@@ -40248,16 +40118,16 @@
       <c r="C154" s="271"/>
       <c r="D154" s="272"/>
       <c r="M154" s="206" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="N154" s="259" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="O154" s="257" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="P154" s="259" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Q154" s="404" t="e">
         <f t="shared" si="9"/>
@@ -40287,16 +40157,16 @@
       <c r="C155" s="271"/>
       <c r="D155" s="272"/>
       <c r="M155" s="206" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="N155" s="259" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="O155" s="257" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="P155" s="259" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Q155" s="404" t="e">
         <f t="shared" si="9"/>
@@ -40326,16 +40196,16 @@
       <c r="C156" s="271"/>
       <c r="D156" s="272"/>
       <c r="M156" s="206" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="N156" s="259" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="O156" s="257" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="P156" s="259" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Q156" s="404" t="e">
         <f t="shared" si="9"/>
@@ -40365,16 +40235,16 @@
       <c r="C157" s="271"/>
       <c r="D157" s="272"/>
       <c r="M157" s="206" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="N157" s="259" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="O157" s="257" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="P157" s="259" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Q157" s="404" t="e">
         <f t="shared" si="9"/>
@@ -40404,16 +40274,16 @@
       <c r="C158" s="271"/>
       <c r="D158" s="272"/>
       <c r="M158" s="206" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="N158" s="259" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="O158" s="257" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="P158" s="259" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Q158" s="404" t="e">
         <f t="shared" si="9"/>
@@ -40436,25 +40306,25 @@
         <v/>
       </c>
       <c r="W158" s="340" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="X158" s="347" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Y158" s="347" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Z158" s="347" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AA158" s="347" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AB158" s="347" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AC158" s="347" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AD158" s="354" t="str">
         <f t="shared" ref="AD158:AD166" si="14">IF(OR(ISBLANK(W158),W158=""),"",Z158/X158)</f>
@@ -40470,16 +40340,16 @@
       <c r="C159" s="271"/>
       <c r="D159" s="272"/>
       <c r="M159" s="206" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="N159" s="259" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="O159" s="257" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="P159" s="259" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Q159" s="404" t="e">
         <f t="shared" si="9"/>
@@ -40502,25 +40372,25 @@
         <v/>
       </c>
       <c r="W159" s="340" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="X159" s="347" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Y159" s="347" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Z159" s="347" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AA159" s="347" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AB159" s="347" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AC159" s="347" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AD159" s="354" t="str">
         <f t="shared" si="14"/>
@@ -40536,16 +40406,16 @@
       <c r="C160" s="271"/>
       <c r="D160" s="272"/>
       <c r="M160" s="206" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="N160" s="259" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="O160" s="257" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="P160" s="259" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Q160" s="404" t="e">
         <f t="shared" si="9"/>
@@ -40568,25 +40438,25 @@
         <v/>
       </c>
       <c r="W160" s="340" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="X160" s="347" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Y160" s="347" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Z160" s="347" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AA160" s="347" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AB160" s="347" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AC160" s="347" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AD160" s="354" t="str">
         <f t="shared" si="14"/>
@@ -40602,16 +40472,16 @@
       <c r="C161" s="271"/>
       <c r="D161" s="272"/>
       <c r="M161" s="206" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="N161" s="259" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="O161" s="257" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="P161" s="259" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Q161" s="404" t="e">
         <f t="shared" si="9"/>
@@ -40634,25 +40504,25 @@
         <v/>
       </c>
       <c r="W161" s="340" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="X161" s="347" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Y161" s="347" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Z161" s="347" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AA161" s="347" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AB161" s="347" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AC161" s="347" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AD161" s="354" t="str">
         <f t="shared" si="14"/>
@@ -40668,16 +40538,16 @@
       <c r="C162" s="271"/>
       <c r="D162" s="272"/>
       <c r="M162" s="206" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="N162" s="259" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="O162" s="257" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="P162" s="259" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Q162" s="404" t="e">
         <f t="shared" si="9"/>
@@ -40700,25 +40570,25 @@
         <v/>
       </c>
       <c r="W162" s="340" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="X162" s="347" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Y162" s="347" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Z162" s="347" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AA162" s="347" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AB162" s="347" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AC162" s="347" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AD162" s="354" t="str">
         <f t="shared" si="14"/>
@@ -40734,16 +40604,16 @@
       <c r="C163" s="271"/>
       <c r="D163" s="272"/>
       <c r="M163" s="206" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="N163" s="259" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="O163" s="257" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="P163" s="259" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Q163" s="404" t="e">
         <f t="shared" si="9"/>
@@ -40766,25 +40636,25 @@
         <v/>
       </c>
       <c r="W163" s="340" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="X163" s="347" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Y163" s="347" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Z163" s="347" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AA163" s="347" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AB163" s="347" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AC163" s="347" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AD163" s="354" t="str">
         <f t="shared" si="14"/>
@@ -40800,16 +40670,16 @@
       <c r="C164" s="271"/>
       <c r="D164" s="272"/>
       <c r="M164" s="206" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="N164" s="259" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="O164" s="257" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="P164" s="259" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Q164" s="404" t="e">
         <f t="shared" si="9"/>
@@ -40832,25 +40702,25 @@
         <v/>
       </c>
       <c r="W164" s="340" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="X164" s="347" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Y164" s="347" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Z164" s="347" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AA164" s="347" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AB164" s="347" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AC164" s="347" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AD164" s="354" t="str">
         <f t="shared" si="14"/>
@@ -40867,16 +40737,16 @@
       <c r="C165" s="271"/>
       <c r="D165" s="353"/>
       <c r="M165" s="206" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="N165" s="259" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="O165" s="257" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="P165" s="259" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Q165" s="404" t="e">
         <f t="shared" si="9"/>
@@ -40899,25 +40769,25 @@
         <v/>
       </c>
       <c r="W165" s="340" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="X165" s="347" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Y165" s="347" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Z165" s="347" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AA165" s="347" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AB165" s="347" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AC165" s="347" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AD165" s="354" t="str">
         <f t="shared" si="14"/>
@@ -40931,16 +40801,16 @@
     <row r="166" spans="1:31" ht="14" thickBot="1" x14ac:dyDescent="0.2">
       <c r="C166" s="271"/>
       <c r="M166" s="209" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="N166" s="260" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="O166" s="258" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="P166" s="260" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Q166" s="404" t="e">
         <f t="shared" si="9"/>
@@ -40963,25 +40833,25 @@
         <v/>
       </c>
       <c r="W166" s="345" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="X166" s="348" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Y166" s="348" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Z166" s="348" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AA166" s="348" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AB166" s="348" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AC166" s="348" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AD166" s="354" t="str">
         <f t="shared" si="14"/>
@@ -40994,16 +40864,16 @@
     </row>
     <row r="167" spans="1:31" ht="13" x14ac:dyDescent="0.15">
       <c r="M167" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="N167" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="O167" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="P167" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Q167" s="404" t="e">
         <f t="shared" si="9"/>
@@ -41018,39 +40888,39 @@
         <v/>
       </c>
       <c r="W167" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="X167" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Y167" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Z167" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AA167" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AB167" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AC167" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="168" spans="1:31" ht="13" x14ac:dyDescent="0.15">
       <c r="M168" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="N168" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="O168" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="P168" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Q168" s="404" t="e">
         <f t="shared" si="9"/>
@@ -41065,39 +40935,39 @@
         <v/>
       </c>
       <c r="W168" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="X168" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Y168" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Z168" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AA168" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AB168" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AC168" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="169" spans="1:31" ht="13" x14ac:dyDescent="0.15">
       <c r="M169" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="N169" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="O169" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="P169" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Q169" s="404" t="e">
         <f t="shared" si="9"/>
@@ -41112,39 +40982,39 @@
         <v/>
       </c>
       <c r="W169" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="X169" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Y169" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Z169" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AA169" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AB169" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AC169" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="170" spans="1:31" ht="13" x14ac:dyDescent="0.15">
       <c r="M170" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="N170" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="O170" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="P170" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Q170" s="404" t="e">
         <f t="shared" si="9"/>
@@ -41159,39 +41029,39 @@
         <v/>
       </c>
       <c r="W170" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="X170" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Y170" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Z170" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AA170" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AB170" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AC170" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="171" spans="1:31" ht="13" x14ac:dyDescent="0.15">
       <c r="M171" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="N171" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="O171" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="P171" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Q171" s="404" t="e">
         <f t="shared" si="9"/>
@@ -41206,39 +41076,39 @@
         <v/>
       </c>
       <c r="W171" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="X171" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Y171" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Z171" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AA171" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AB171" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AC171" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="172" spans="1:31" ht="13" x14ac:dyDescent="0.15">
       <c r="M172" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="N172" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="O172" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="P172" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Q172" s="404" t="e">
         <f t="shared" si="9"/>
@@ -41253,39 +41123,39 @@
         <v/>
       </c>
       <c r="W172" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="X172" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Y172" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Z172" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AA172" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AB172" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AC172" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="173" spans="1:31" ht="13" x14ac:dyDescent="0.15">
       <c r="M173" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="N173" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="O173" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="P173" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Q173" s="404" t="e">
         <f t="shared" si="9"/>
@@ -41300,39 +41170,39 @@
         <v/>
       </c>
       <c r="W173" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="X173" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Y173" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Z173" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AA173" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AB173" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AC173" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="174" spans="1:31" ht="13" x14ac:dyDescent="0.15">
       <c r="M174" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="N174" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="O174" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="P174" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Q174" s="404" t="e">
         <f t="shared" si="9"/>
@@ -41347,39 +41217,39 @@
         <v/>
       </c>
       <c r="W174" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="X174" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Y174" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Z174" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AA174" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AB174" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AC174" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="175" spans="1:31" ht="13" x14ac:dyDescent="0.15">
       <c r="M175" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="N175" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="O175" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="P175" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Q175" s="404" t="e">
         <f t="shared" si="9"/>
@@ -41394,39 +41264,39 @@
         <v/>
       </c>
       <c r="W175" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="X175" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Y175" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Z175" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AA175" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AB175" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AC175" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="176" spans="1:31" ht="13" x14ac:dyDescent="0.15">
       <c r="M176" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="N176" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="O176" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="P176" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Q176" s="404" t="e">
         <f t="shared" si="9"/>
@@ -41441,39 +41311,39 @@
         <v/>
       </c>
       <c r="W176" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="X176" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Y176" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Z176" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AA176" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AB176" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AC176" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="177" spans="13:29" ht="13" x14ac:dyDescent="0.15">
       <c r="M177" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="N177" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="O177" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="P177" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Q177" s="404" t="e">
         <f t="shared" ref="Q177:Q197" si="16">P177/O177</f>
@@ -41488,39 +41358,39 @@
         <v/>
       </c>
       <c r="W177" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="X177" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Y177" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Z177" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AA177" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AB177" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AC177" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="178" spans="13:29" ht="13" x14ac:dyDescent="0.15">
       <c r="M178" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="N178" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="O178" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="P178" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Q178" s="404" t="e">
         <f t="shared" si="16"/>
@@ -41535,39 +41405,39 @@
         <v/>
       </c>
       <c r="W178" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="X178" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Y178" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Z178" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AA178" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AB178" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AC178" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="179" spans="13:29" ht="13" x14ac:dyDescent="0.15">
       <c r="M179" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="N179" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="O179" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="P179" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Q179" s="404" t="e">
         <f t="shared" si="16"/>
@@ -41582,39 +41452,39 @@
         <v/>
       </c>
       <c r="W179" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="X179" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Y179" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Z179" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AA179" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AB179" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AC179" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="180" spans="13:29" ht="13" x14ac:dyDescent="0.15">
       <c r="M180" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="N180" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="O180" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="P180" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Q180" s="404" t="e">
         <f t="shared" si="16"/>
@@ -41629,39 +41499,39 @@
         <v/>
       </c>
       <c r="W180" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="X180" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Y180" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Z180" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AA180" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AB180" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AC180" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="181" spans="13:29" ht="13" x14ac:dyDescent="0.15">
       <c r="M181" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="N181" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="O181" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="P181" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Q181" s="404" t="e">
         <f t="shared" si="16"/>
@@ -41676,39 +41546,39 @@
         <v/>
       </c>
       <c r="W181" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="X181" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Y181" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Z181" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AA181" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AB181" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AC181" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="182" spans="13:29" ht="13" x14ac:dyDescent="0.15">
       <c r="M182" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="N182" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="O182" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="P182" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Q182" s="404" t="e">
         <f t="shared" si="16"/>
@@ -41723,39 +41593,39 @@
         <v/>
       </c>
       <c r="W182" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="X182" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Y182" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Z182" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AA182" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AB182" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AC182" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="183" spans="13:29" ht="13" x14ac:dyDescent="0.15">
       <c r="M183" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="N183" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="O183" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="P183" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Q183" s="404" t="e">
         <f t="shared" si="16"/>
@@ -41770,39 +41640,39 @@
         <v/>
       </c>
       <c r="W183" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="X183" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Y183" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Z183" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AA183" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AB183" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AC183" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="184" spans="13:29" ht="13" x14ac:dyDescent="0.15">
       <c r="M184" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="N184" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="O184" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="P184" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Q184" s="404" t="e">
         <f t="shared" si="16"/>
@@ -41817,39 +41687,39 @@
         <v/>
       </c>
       <c r="W184" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="X184" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Y184" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Z184" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AA184" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AB184" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AC184" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="185" spans="13:29" ht="13" x14ac:dyDescent="0.15">
       <c r="M185" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="N185" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="O185" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="P185" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Q185" s="404" t="e">
         <f t="shared" si="16"/>
@@ -41864,39 +41734,39 @@
         <v/>
       </c>
       <c r="W185" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="X185" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Y185" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Z185" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AA185" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AB185" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AC185" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="186" spans="13:29" ht="13" x14ac:dyDescent="0.15">
       <c r="M186" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="N186" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="O186" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="P186" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Q186" s="404" t="e">
         <f t="shared" si="16"/>
@@ -41911,39 +41781,39 @@
         <v/>
       </c>
       <c r="W186" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="X186" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Y186" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Z186" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AA186" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AB186" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AC186" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="187" spans="13:29" ht="13" x14ac:dyDescent="0.15">
       <c r="M187" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="N187" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="O187" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="P187" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Q187" s="404" t="e">
         <f t="shared" si="16"/>
@@ -41958,39 +41828,39 @@
         <v/>
       </c>
       <c r="W187" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="X187" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Y187" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Z187" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AA187" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AB187" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AC187" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="188" spans="13:29" ht="13" x14ac:dyDescent="0.15">
       <c r="M188" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="N188" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="O188" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="P188" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Q188" s="404" t="e">
         <f t="shared" si="16"/>
@@ -42005,39 +41875,39 @@
         <v/>
       </c>
       <c r="W188" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="X188" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Y188" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Z188" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AA188" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AB188" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AC188" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="189" spans="13:29" ht="13" x14ac:dyDescent="0.15">
       <c r="M189" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="N189" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="O189" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="P189" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Q189" s="404" t="e">
         <f t="shared" si="16"/>
@@ -42052,39 +41922,39 @@
         <v/>
       </c>
       <c r="W189" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="X189" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Y189" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Z189" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AA189" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AB189" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AC189" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="190" spans="13:29" ht="13" x14ac:dyDescent="0.15">
       <c r="M190" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="N190" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="O190" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="P190" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Q190" s="404" t="e">
         <f t="shared" si="16"/>
@@ -42099,39 +41969,39 @@
         <v/>
       </c>
       <c r="W190" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="X190" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Y190" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Z190" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AA190" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AB190" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AC190" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="191" spans="13:29" ht="13" x14ac:dyDescent="0.15">
       <c r="M191" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="N191" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="O191" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="P191" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Q191" s="404" t="e">
         <f t="shared" si="16"/>
@@ -42146,39 +42016,39 @@
         <v/>
       </c>
       <c r="W191" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="X191" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Y191" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Z191" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AA191" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AB191" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AC191" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="192" spans="13:29" ht="13" x14ac:dyDescent="0.15">
       <c r="M192" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="N192" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="O192" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="P192" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Q192" s="404" t="e">
         <f t="shared" si="16"/>
@@ -42193,39 +42063,39 @@
         <v/>
       </c>
       <c r="W192" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="X192" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Y192" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Z192" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AA192" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AB192" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AC192" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="193" spans="8:29" ht="13" x14ac:dyDescent="0.15">
       <c r="M193" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="N193" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="O193" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="P193" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Q193" s="404" t="e">
         <f t="shared" si="16"/>
@@ -42240,39 +42110,39 @@
         <v/>
       </c>
       <c r="W193" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="X193" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Y193" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Z193" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AA193" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AB193" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AC193" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="194" spans="8:29" ht="13" x14ac:dyDescent="0.15">
       <c r="M194" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="N194" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="O194" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="P194" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Q194" s="404" t="e">
         <f t="shared" si="16"/>
@@ -42287,39 +42157,39 @@
         <v/>
       </c>
       <c r="W194" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="X194" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Y194" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Z194" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AA194" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AB194" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AC194" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="195" spans="8:29" ht="13" x14ac:dyDescent="0.15">
       <c r="M195" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="N195" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="O195" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="P195" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Q195" s="404" t="e">
         <f t="shared" si="16"/>
@@ -42334,39 +42204,39 @@
         <v/>
       </c>
       <c r="W195" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="X195" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Y195" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Z195" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AA195" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AB195" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AC195" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="196" spans="8:29" ht="13" x14ac:dyDescent="0.15">
       <c r="M196" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="N196" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="O196" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="P196" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Q196" s="404" t="e">
         <f t="shared" si="16"/>
@@ -42381,39 +42251,39 @@
         <v/>
       </c>
       <c r="W196" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="X196" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Y196" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Z196" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AA196" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AB196" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AC196" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="197" spans="8:29" ht="13" x14ac:dyDescent="0.15">
       <c r="M197" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="N197" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="O197" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="P197" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Q197" s="404" t="e">
         <f t="shared" si="16"/>
@@ -42428,25 +42298,25 @@
         <v/>
       </c>
       <c r="W197" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="X197" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Y197" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Z197" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AA197" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AB197" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AC197" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="198" spans="8:29" x14ac:dyDescent="0.15">
